--- a/reports/pdf_change_20260915.xlsx
+++ b/reports/pdf_change_20260915.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,11 +60,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +93,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -156,10 +165,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -551,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,394억   ·   현금 37억(0.8%)      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,394억      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -731,7 +747,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,371억   ·   현금 43억(1.3%)      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,371억      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -755,7 +771,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,459억   ·   현금 40억(1.6%)      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,459억      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -779,7 +795,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,915억   ·   현금 17억(0.9%)      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,915억      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -801,75 +817,221 @@
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="17" t="n"/>
-      <c r="J19" s="17" t="n"/>
-      <c r="K19" s="17" t="n"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 4억(0.9%)      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 1억(0.4%)      당일 2026-09-15  vs  전영업일 2026-09-14      매수 1종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>48762000</v>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>2.65%→2.83%</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>88→94</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>-106</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>-34799800</v>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>2.98%→2.86%</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>2,452→2,346</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>-36652000</v>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>5.37%→5.23%</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>869→847</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억      당일 2026-09-15  vs  전영업일 2026-09-14      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="17" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="20" t="n"/>
+      <c r="K28" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A22:K22"/>
+  <mergeCells count="17">
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A28:K28"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>

--- a/reports/pdf_change_20260915.xlsx
+++ b/reports/pdf_change_20260915.xlsx
@@ -819,7 +819,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 1억(0.4%)      당일 2026-09-15  vs  전영업일 2026-09-14      매수 1종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억      당일 2026-09-15  vs  전영업일 2026-09-14      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
